--- a/docs/StructureDefinition-BRRegistroAtendimentoClinico.xlsx
+++ b/docs/StructureDefinition-BRRegistroAtendimentoClinico.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -380,7 +380,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1062,7 +1062,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1140,7 +1140,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1213,7 +1213,7 @@
     <t>Composition.subject.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1250,7 +1250,7 @@
     <t>Composition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1529,7 +1529,7 @@
     <t>Composition.attester.party</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson|Practitioner|PractitionerRole|Organization)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1753,7 +1753,7 @@
     <t>Composition.event.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1836,13 +1836,13 @@
     <t>Classification of a section of a composition/document.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/doc-section-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/doc-section-codes|4.0.1</t>
   </si>
   <si>
     <t>Composition.section.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Device|Patient|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1928,7 +1928,7 @@
     <t>What order applies to the items in the entry.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-order</t>
+    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
@@ -1974,7 +1974,7 @@
     <t>If a section is empty, why it is empty.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-empty-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
@@ -3164,7 +3164,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>159</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>172</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>195</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>245</v>
       </c>
@@ -6214,7 +6214,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>256</v>
       </c>
@@ -7273,7 +7273,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>265</v>
       </c>
@@ -7624,7 +7624,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>277</v>
       </c>
@@ -7971,7 +7971,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>289</v>
       </c>
@@ -8552,7 +8552,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>306</v>
       </c>
@@ -9133,7 +9133,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>313</v>
       </c>
@@ -11469,7 +11469,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>408</v>
       </c>
@@ -11588,7 +11588,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>419</v>
       </c>
@@ -13345,7 +13345,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>444</v>
       </c>
@@ -18386,7 +18386,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
         <v>642</v>
       </c>
@@ -19681,7 +19681,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="143" hidden="true">
+    <row r="143">
       <c r="A143" t="s" s="2">
         <v>656</v>
       </c>
@@ -20734,7 +20734,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="152" hidden="true">
+    <row r="152">
       <c r="A152" t="s" s="2">
         <v>672</v>
       </c>
@@ -22029,7 +22029,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="163" hidden="true">
+    <row r="163">
       <c r="A163" t="s" s="2">
         <v>685</v>
       </c>
@@ -22378,7 +22378,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="166" hidden="true">
+    <row r="166">
       <c r="A166" t="s" s="2">
         <v>689</v>
       </c>
@@ -22846,7 +22846,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="170" hidden="true">
+    <row r="170">
       <c r="A170" t="s" s="2">
         <v>693</v>
       </c>
@@ -24373,7 +24373,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="183" hidden="true">
+    <row r="183">
       <c r="A183" t="s" s="2">
         <v>718</v>
       </c>
@@ -25668,7 +25668,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="194" hidden="true">
+    <row r="194">
       <c r="A194" t="s" s="2">
         <v>731</v>
       </c>
@@ -26721,7 +26721,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="203" hidden="true">
+    <row r="203">
       <c r="A203" t="s" s="2">
         <v>741</v>
       </c>
@@ -29069,7 +29069,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="223" hidden="true">
+    <row r="223">
       <c r="A223" t="s" s="2">
         <v>763</v>
       </c>
@@ -31417,7 +31417,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="243" hidden="true">
+    <row r="243">
       <c r="A243" t="s" s="2">
         <v>785</v>
       </c>
@@ -34703,7 +34703,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="271" hidden="true">
+    <row r="271">
       <c r="A271" t="s" s="2">
         <v>823</v>
       </c>
@@ -37051,7 +37051,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="291" hidden="true">
+    <row r="291">
       <c r="A291" t="s" s="2">
         <v>845</v>
       </c>
@@ -39401,12 +39401,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO310">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
